--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484031_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484031_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0832</v>
+        <v>4.3208</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9316</v>
+        <v>5.8757</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1516</v>
+        <v>-1.5549</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6232</v>
+        <v>5.3808</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5414</v>
+        <v>2.6705</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0818</v>
+        <v>2.7103</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5744</v>
+        <v>7.0663</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7218</v>
+        <v>3.8509</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8525</v>
+        <v>3.2155</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9511</v>
+        <v>-1.6855</v>
       </c>
       <c r="N2" t="n">
         <v>-1.1804</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5051</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5952</v>
+        <v>-1.8535</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3492</v>
+        <v>-0.4647</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.754</v>
+        <v>-1.3888</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7483</v>
+        <v>3.4763</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3032</v>
+        <v>3.6052</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5549</v>
+        <v>-0.129</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3808</v>
+        <v>2.6232</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6705</v>
+        <v>1.5414</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7103</v>
+        <v>1.0818</v>
       </c>
       <c r="J3" t="n">
-        <v>7.0663</v>
+        <v>4.5744</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8509</v>
+        <v>2.7218</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2155</v>
+        <v>1.8525</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6855</v>
+        <v>-1.9511</v>
       </c>
       <c r="N3" t="n">
         <v>-1.1804</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5051</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.426</v>
+        <v>-1.0118</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0372</v>
+        <v>0.0228</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3888</v>
+        <v>-1.0346</v>
       </c>
       <c r="V3" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.266</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5834</v>
+        <v>0.8155</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.105</v>
+        <v>0.099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6884</v>
+        <v>0.7165</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1389</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.469</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4761</v>
+        <v>-0.272</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2251</v>
+        <v>-0.197</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3619</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.245</v>
+        <v>-0.037</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5635</v>
+        <v>2.4218</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3185</v>
+        <v>-2.4588</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1173</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4393</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3173</v>
+        <v>-0.459</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.122</v>
+        <v>-0.2622</v>
       </c>
       <c r="V5" t="n">
         <v>0.6032</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0866</v>
+        <v>-1.6888</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4005</v>
+        <v>-0.0708</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3139</v>
+        <v>-1.618</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8021</v>
+        <v>0.2408</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7363</v>
+        <v>-2.0213</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9342</v>
+        <v>2.2621</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1116</v>
+        <v>2.5312</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.3526</v>
+        <v>0.0361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.241</v>
+        <v>2.4951</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3095</v>
+        <v>-2.2904</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3837</v>
+        <v>-2.0573</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6932</v>
+        <v>-0.2331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6292</v>
+        <v>-1.8337</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3775</v>
+        <v>-0.8841</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7483</v>
+        <v>-0.9495</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9057</v>
+        <v>-0.096</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2311</v>
+        <v>-0.3619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5317</v>
+        <v>-3.1069</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7453</v>
+        <v>-3.4208</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7864</v>
+        <v>0.3139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2408</v>
+        <v>-1.8021</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0213</v>
+        <v>-2.7363</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2621</v>
+        <v>0.9342</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5312</v>
+        <v>-2.1116</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0361</v>
+        <v>-2.3526</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4951</v>
+        <v>0.241</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2904</v>
+        <v>0.3095</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0573</v>
+        <v>-0.3837</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2331</v>
+        <v>0.6932</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.6765</v>
+        <v>-0.3911</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5586</v>
+        <v>0.3572</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1179</v>
+        <v>-0.7483</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.096</v>
+        <v>-1.9057</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3619</v>
+        <v>-1.2311</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.6334</v>
+        <v>-7.5023</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.8473</v>
+        <v>-4.9687</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7861</v>
+        <v>-2.5336</v>
       </c>
       <c r="G8" t="n">
         <v>-7.226</v>
@@ -1078,13 +1078,13 @@
         <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6487</v>
+        <v>-1.5176</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4112</v>
+        <v>-0.5327</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2375</v>
+        <v>-0.985</v>
       </c>
       <c r="V8" t="n">
         <v>0.8445</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.672599999999999</v>
+        <v>-8.2302</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.9262</v>
+        <v>-6.4557</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7464</v>
+        <v>-1.7745</v>
       </c>
       <c r="G9" t="n">
         <v>-7.0171</v>
@@ -1156,13 +1156,13 @@
         <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9402</v>
+        <v>-1.4978</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4112</v>
+        <v>-0.9408</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.529</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3024</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.26439999999999</v>
+        <v>-11.9526</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.225999999999997</v>
+        <v>-2.914300000000001</v>
       </c>
       <c r="F10" t="n">
         <v>-9.038399999999999</v>
@@ -1234,13 +1234,13 @@
         <v>15.8707</v>
       </c>
       <c r="S10" t="n">
-        <v>-9.6074</v>
+        <v>-9.2958</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.4849</v>
+        <v>-3.1733</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.1226</v>
+        <v>-6.1224</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5438</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.2906</v>
+        <v>7.8086</v>
       </c>
       <c r="E11" t="n">
-        <v>9.8209</v>
+        <v>8.086399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5303</v>
+        <v>-0.2778</v>
       </c>
       <c r="G11" t="n">
         <v>7.5711</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1839</v>
+        <v>1.7019</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2083</v>
+        <v>1.4738</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0245</v>
+        <v>0.228</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8692</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6244</v>
+        <v>4.962</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1482</v>
+        <v>3.6584</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4762</v>
+        <v>1.3036</v>
       </c>
       <c r="G12" t="n">
         <v>4.0828</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0015</v>
+        <v>1.3391</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1813</v>
+        <v>0.3289</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1828</v>
+        <v>1.0102</v>
       </c>
       <c r="V12" t="n">
         <v>0.532</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1174</v>
+        <v>1.8624</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2948</v>
+        <v>2.2718</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8226</v>
+        <v>-0.4093</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06610000000000001</v>
+        <v>1.2484</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7969000000000001</v>
+        <v>1.8237</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7308</v>
+        <v>-0.5753</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0254</v>
+        <v>2.8077</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5709</v>
+        <v>2.1976</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4545</v>
+        <v>0.6101</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9593</v>
+        <v>-1.5593</v>
       </c>
       <c r="N13" t="n">
-        <v>0.226</v>
+        <v>-0.3739</v>
       </c>
       <c r="O13" t="n">
         <v>-1.1853</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9837</v>
+        <v>1.614</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5905</v>
+        <v>0.8447</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3933</v>
+        <v>0.7693</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3373</v>
+        <v>-0.6032</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3373</v>
+        <v>0.6032</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9832</v>
+        <v>1.6753</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3541</v>
+        <v>0.9663</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6291</v>
+        <v>0.709</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5566</v>
@@ -1546,13 +1546,13 @@
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3253</v>
+        <v>1.0174</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1303</v>
+        <v>0.4819</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4556</v>
+        <v>0.5355</v>
       </c>
       <c r="V14" t="n">
         <v>2.4129</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6963</v>
+        <v>1.2791</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8401</v>
+        <v>0.3765</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5364</v>
+        <v>0.9026</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3884</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6581</v>
+        <v>-0.7308</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6935</v>
+        <v>1.0254</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0484</v>
+        <v>0.5709</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6451</v>
+        <v>0.4545</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3051</v>
+        <v>-0.9593</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3181</v>
+        <v>0.226</v>
       </c>
       <c r="O15" t="n">
-        <v>0.013</v>
+        <v>-1.1853</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5871</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2204</v>
+        <v>2.1454</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5498</v>
+        <v>1.6722</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7702</v>
+        <v>0.4732</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6745</v>
+        <v>-0.3373</v>
       </c>
       <c r="W15" t="n">
+        <v>-0.3373</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.6745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6185</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0474</v>
+        <v>-0.534</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4289</v>
+        <v>1.476</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2484</v>
+        <v>1.3884</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8237</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5753</v>
+        <v>0.6581</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8077</v>
+        <v>1.6935</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1976</v>
+        <v>1.0484</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6101</v>
+        <v>0.6451</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5593</v>
+        <v>-0.3051</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3739</v>
+        <v>-0.3181</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1853</v>
+        <v>0.013</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3701</v>
+        <v>0.4662</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3797</v>
+        <v>-0.2437</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7497</v>
+        <v>0.7099</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6032</v>
+        <v>0.6745</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.52</v>
+        <v>0.4103</v>
       </c>
       <c r="E17" t="n">
-        <v>0.581</v>
+        <v>0.2749</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0609</v>
+        <v>0.1355</v>
       </c>
       <c r="G17" t="n">
         <v>0.0433</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2783</v>
+        <v>0.1686</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5555</v>
+        <v>0.2494</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2772</v>
+        <v>-0.0808</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4511</v>
+        <v>-0.9871</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3081</v>
+        <v>-2.0452</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.143</v>
+        <v>1.058</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8368</v>
+        <v>-1.93</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8744</v>
+        <v>-0.5696</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0376</v>
+        <v>-1.3604</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8693</v>
+        <v>-1.846</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.03</v>
+        <v>-1.1333</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1606</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0325</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1556</v>
+        <v>0.5637</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.123</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>-0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1873</v>
+        <v>0.3316</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5532</v>
+        <v>0.5782</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6342</v>
+        <v>-0.2467</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1383</v>
+        <v>-2.0344</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5553</v>
+        <v>-1.7904</v>
       </c>
       <c r="F19" t="n">
-        <v>0.417</v>
+        <v>-0.244</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.93</v>
+        <v>-1.0202</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5696</v>
+        <v>-0.923</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3604</v>
+        <v>-0.0973</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.846</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1333</v>
+        <v>0.2016</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7127</v>
+        <v>-0.1103</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-1.1116</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5637</v>
+        <v>-1.1246</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5952</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8196</v>
+        <v>0.8389</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1021</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8877</v>
+        <v>0.7368</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2065</v>
+        <v>-0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9969</v>
+        <v>-2.2936</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5046</v>
+        <v>-2.2264</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4923</v>
+        <v>-0.0673</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0202</v>
+        <v>-1.8368</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.923</v>
+        <v>-1.8744</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0973</v>
+        <v>0.0376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09130000000000001</v>
+        <v>-1.8693</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2016</v>
+        <v>-2.03</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1103</v>
+        <v>0.1606</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1116</v>
+        <v>0.0325</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1246</v>
+        <v>0.1556</v>
       </c>
       <c r="O20" t="n">
-        <v>0.013</v>
+        <v>-0.123</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5871</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1236</v>
+        <v>1.3448</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6121</v>
+        <v>0.6349</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4885</v>
+        <v>0.7099</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>12.2641</v>
+        <v>13.6246</v>
       </c>
       <c r="E21" t="n">
         <v>9.0383</v>
       </c>
       <c r="F21" t="n">
-        <v>3.225899999999999</v>
+        <v>4.5863</v>
       </c>
       <c r="G21" t="n">
         <v>8.0565</v>
@@ -2071,13 +2071,13 @@
         <v>10.2377</v>
       </c>
       <c r="L21" t="n">
-        <v>4.468700000000001</v>
+        <v>4.4687</v>
       </c>
       <c r="M21" t="n">
-        <v>-6.649999999999999</v>
+        <v>-6.65</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7881999999999999</v>
+        <v>-0.7882</v>
       </c>
       <c r="O21" t="n">
         <v>-5.861600000000001</v>
@@ -2089,16 +2089,16 @@
         <v>-15.8704</v>
       </c>
       <c r="R21" t="n">
-        <v>8.9274</v>
+        <v>8.927400000000002</v>
       </c>
       <c r="S21" t="n">
-        <v>9.6073</v>
+        <v>10.9679</v>
       </c>
       <c r="T21" t="n">
         <v>6.1224</v>
       </c>
       <c r="U21" t="n">
-        <v>3.4849</v>
+        <v>4.8453</v>
       </c>
       <c r="V21" t="n">
         <v>1.5437</v>
